--- a/Madona_A_Analysis.xlsx
+++ b/Madona_A_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\madon\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3EFD574-E4D0-4B7E-8D1C-FD7A359124E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BD1C07-1B2F-4BE4-BC5A-B534E1613A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1116" windowWidth="23040" windowHeight="11124" activeTab="1" xr2:uid="{805A4D93-7ACE-4C04-98C5-48489EDDA245}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="70">
   <si>
     <t>Claim</t>
   </si>
@@ -541,6 +541,18 @@
   </si>
   <si>
     <t>All six orders use USD, a valid 3-letter code</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Included both pages despite page 1's has_more saying false, because the cursor still returned 2 more real orders (ord_1005, ord_1006). If only page 1 were used, revenue would be $146.61.</t>
+  </si>
+  <si>
+    <t>Task 1: Docs vs Data — Meridian Orders API (Madona A)</t>
+  </si>
+  <si>
+    <t>Task 2: Revenue Calculation — Meridian Orders API (Madona A)</t>
   </si>
 </sst>
 </file>
@@ -550,7 +562,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -591,6 +603,13 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -601,12 +620,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="-0.249977111117893"/>
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -629,6 +648,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -640,13 +668,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -662,9 +683,20 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -980,258 +1012,270 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DED080D-4260-428C-801B-2AD2F84454B9}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="57" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="56.33203125" customWidth="1"/>
     <col min="4" max="4" width="36.88671875" customWidth="1"/>
     <col min="5" max="5" width="44.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="6" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:5" s="13" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+    </row>
+    <row r="2" spans="1:5" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
+    <row r="3" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D2" s="7" t="b">
+      <c r="D3" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E3" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
+    <row r="4" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="7" t="b">
+      <c r="D4" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E4" s="4" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="83.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+    <row r="5" spans="1:5" ht="83.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="b">
+      <c r="D5" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E5" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="7" t="b">
+      <c r="D6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E6" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="42" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+    <row r="7" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A7" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="7" t="b">
+      <c r="D7" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E7" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="42" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
+    <row r="8" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A8" s="3">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="D7" s="7" t="b">
+      <c r="D8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E8" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="42" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
+    <row r="9" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A9" s="3">
         <v>7</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="7" t="b">
+      <c r="D9" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E9" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
+    <row r="10" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="3">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="7" t="b">
+      <c r="D10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E10" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="55.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
+    <row r="11" spans="1:5" ht="55.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="3">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="7" t="b">
+      <c r="D11" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E11" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="55.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
+    <row r="12" spans="1:5" ht="55.8" x14ac:dyDescent="0.3">
+      <c r="A12" s="3">
         <v>10</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="7" t="b">
+      <c r="D12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="9" t="s">
+      <c r="E12" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="42" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
+    <row r="13" spans="1:5" ht="42" x14ac:dyDescent="0.3">
+      <c r="A13" s="3">
         <v>11</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="7" t="b">
+      <c r="D13" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E13" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
+    <row r="14" spans="1:5" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="3">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B14" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="7" t="b">
+      <c r="D14" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="E13" s="9" t="s">
+      <c r="E14" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
-      <c r="B15" s="4"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D2E9BB7-FEEE-4532-9DFF-2FFFB9E4A474}">
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.109375" customWidth="1"/>
@@ -1242,177 +1286,198 @@
     <col min="6" max="7" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:6" ht="20.399999999999999" x14ac:dyDescent="0.35">
+      <c r="A1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" s="9" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B2" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D2" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E2" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F2" s="12" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="8">
+      <c r="D3" s="3">
         <v>5470</v>
       </c>
-      <c r="E2" s="8">
+      <c r="E3" s="3">
         <v>5470</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F3" s="3" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="8">
+      <c r="D4" s="3">
         <v>2381</v>
       </c>
-      <c r="E3" s="8">
+      <c r="E4" s="3">
         <v>2381</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F4" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="42" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="5" spans="1:6" ht="42" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D5" s="3">
         <v>10233</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E5" s="3">
         <v>0</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F5" s="4" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="55.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="6" spans="1:6" ht="55.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="8">
+      <c r="D6" s="3">
         <v>6810</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E6" s="3">
         <v>6810</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F6" s="4" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="28.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="7" spans="1:6" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D7" s="3">
         <v>2547</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E7" s="3">
         <v>2547</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F7" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="55.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="8" spans="1:6" ht="55.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D8" s="3">
         <v>53.62</v>
       </c>
-      <c r="E7" s="8">
-        <f>(D7*100)</f>
+      <c r="E8" s="3">
+        <f>(D8*100)</f>
         <v>5362</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F8" s="4" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E8" s="11">
-        <f>SUMIF(C2:C7,"Yes",E2:E7)</f>
+      <c r="E9" s="6">
+        <f>SUMIF(C3:C8,"Yes",E3:E8)</f>
         <v>22570</v>
       </c>
-      <c r="F8" s="10"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11" t="s">
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E9" s="12">
-        <f>(E8/100)</f>
+      <c r="E10" s="7">
+        <f>(E9/100)</f>
         <v>225.7</v>
       </c>
-      <c r="F9" s="10"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
+      <c r="F10" s="5"/>
+    </row>
+    <row r="12" spans="1:6" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="D12" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
